--- a/output/pdf_financials_xlsx/MAXM.xlsx
+++ b/output/pdf_financials_xlsx/MAXM.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.02681</v>
       </c>
     </row>
     <row r="13">
@@ -787,7 +787,7 @@
         <v>-0.089353</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.605752</v>
+        <v>-2.632562</v>
       </c>
     </row>
     <row r="28">
@@ -813,7 +813,7 @@
         <v>-0.089353</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.605752</v>
+        <v>-2.632562</v>
       </c>
     </row>
     <row r="30">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">

--- a/output/pdf_financials_xlsx/MAXM.xlsx
+++ b/output/pdf_financials_xlsx/MAXM.xlsx
@@ -876,15 +876,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.700088</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>5.096415</v>
       </c>
     </row>
     <row r="35">
@@ -893,15 +889,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -910,15 +902,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.700088</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>5.096415</v>
       </c>
     </row>
     <row r="37">
@@ -927,15 +915,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.133611</v>
       </c>
     </row>
     <row r="38">
@@ -944,15 +928,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -961,15 +941,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -978,15 +954,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -995,15 +967,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.133611</v>
       </c>
     </row>
     <row r="42">
@@ -1012,15 +980,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1029,15 +993,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1046,15 +1006,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1063,15 +1019,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1080,15 +1032,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1097,15 +1045,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1114,15 +1058,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.578225</v>
       </c>
     </row>
     <row r="49">
@@ -1131,15 +1071,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.707778</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>5.808251</v>
       </c>
     </row>
     <row r="50">
@@ -1148,15 +1084,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1165,15 +1097,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1182,15 +1110,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1199,15 +1123,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1216,15 +1136,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1250,15 +1166,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1267,15 +1179,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1284,15 +1192,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1301,15 +1205,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1318,15 +1218,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1335,15 +1231,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.592381</v>
       </c>
     </row>
     <row r="62">
@@ -1352,15 +1244,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.592381</v>
       </c>
     </row>
     <row r="63">
@@ -1369,15 +1257,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>0.722778</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6.400632</v>
       </c>
     </row>
     <row r="64">
@@ -1386,15 +1270,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1403,15 +1283,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1420,15 +1296,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1437,15 +1309,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1454,15 +1322,11 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.054903</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.087322</v>
       </c>
     </row>
     <row r="69">
@@ -1471,15 +1335,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1488,15 +1348,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1505,15 +1361,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1522,15 +1374,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1539,15 +1387,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1556,15 +1400,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1573,15 +1413,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1607,15 +1443,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1624,15 +1456,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1641,15 +1469,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1675,15 +1499,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1692,15 +1512,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1709,15 +1525,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1726,15 +1538,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1743,15 +1551,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1777,15 +1581,11 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.069782</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.087322</v>
       </c>
     </row>
     <row r="88">
@@ -1794,15 +1594,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.406951</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>8.130081000000001</v>
       </c>
     </row>
     <row r="89">
@@ -1811,15 +1607,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1828,15 +1620,11 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-0.089353</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>-2.695105</v>
       </c>
     </row>
     <row r="91">
@@ -1845,15 +1633,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1862,15 +1646,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0.335398</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0.878134</v>
       </c>
     </row>
     <row r="93">
@@ -1879,15 +1659,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1896,15 +1672,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.652996</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>6.31331</v>
       </c>
     </row>
     <row r="95">
@@ -1913,15 +1685,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1930,15 +1698,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.652996</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>6.31331</v>
       </c>
     </row>
     <row r="97">
@@ -1947,15 +1711,11 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.9034530658099721</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.9863572847181341</v>
       </c>
     </row>
     <row r="98">
@@ -2461,7 +2221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2505,431 +2265,439 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>Vancouver, B.C.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="5" t="n">
-        <v>0.002024</v>
+        <v>0.002026</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1.1e-05</v>
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>-0.089353</v>
+        <v>0.700088</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-2.605752</v>
+        <v>5.096415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Accrued interest income</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.00769</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.017524</v>
+        <v>0.133611</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="5" t="n">
-        <v>-0.121246</v>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0.014879</v>
+        <v>0.578225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.707778</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.604962</v>
+        <v>5.808251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Resource properties 5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" s="5" t="n">
-        <v>-0.00769</v>
+        <v>0.015</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0.108397</v>
+        <v>0.592381</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.722778</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.578225</v>
+        <v>6.400632</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Accounts payable and accrued liabilities 8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
         <v>0.054903</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.032419</v>
+        <v>0.087322</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Flow-through premium liability 6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="5" t="n">
-        <v>-0.163386</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-2.687396</v>
+        <v>0.014879</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Investing activity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Acquisition of resource properties</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
-        <v>-0.015</v>
+        <v>0.069782</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-0.385</v>
+        <v>0.087322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Investing activity</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cash used in investing activity</t>
+          <t>Share capital 7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.015</v>
+        <v>0.406951</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.385</v>
+        <v>8.130081000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Proceeds from private placement of units</t>
+          <t>Shares to be issued 7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" s="5" t="n">
-        <v>0.910035</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3.60577</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Proceeds from the issuance of flow-through shares</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.335398</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>2.6005</v>
+        <v>0.878134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Proceeds from shares to be issued</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-0.089353</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.0002</v>
+        <v>-2.695105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of stock option</t>
+          <t>Total shareholders’ equity</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.652996</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.06525</v>
+        <v>6.31331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of warrants</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total liabilities and shareholders’ equity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.722778</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1.606052</v>
+        <v>6.400632</v>
       </c>
     </row>
     <row r="18">
@@ -2940,24 +2708,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Period from</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" s="5" t="n">
-        <v>-0.031561</v>
+        <v>0.002024</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.409049</v>
+        <v>1.1e-05</v>
       </c>
     </row>
     <row r="19">
@@ -2968,24 +2732,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
+          <t>Net loss for the period</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.878474</v>
+        <v>-0.089353</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>7.468723</v>
+        <v>-2.605752</v>
       </c>
     </row>
     <row r="20">
@@ -2996,24 +2760,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Change in cash</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0.700088</v>
+          <t>Accrued interest income</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>4.396327</v>
+        <v>-0.017524</v>
       </c>
     </row>
     <row r="21">
@@ -3024,26 +2786,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of the period</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization of flow-through premium</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>-0.121246</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.700088</v>
+        <v>-0.014879</v>
       </c>
     </row>
     <row r="22">
@@ -3054,24 +2810,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of the period</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0.700088</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>5.096415</v>
+        <v>0.604962</v>
       </c>
     </row>
     <row r="23">
@@ -3082,22 +2840,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cash received from interest</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.00769</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.009286000000000001</v>
+        <v>-0.108397</v>
       </c>
     </row>
     <row r="24">
@@ -3108,24 +2868,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cash paid for income taxes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="5" t="n">
+        <v>-0.578225</v>
       </c>
     </row>
     <row r="25">
@@ -3136,24 +2898,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cash paid for the interest</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.054903</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.032419</v>
       </c>
     </row>
     <row r="26">
@@ -3164,22 +2926,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fair value of finders warrants issued</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-0.163386</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.444085</v>
+        <v>-2.687396</v>
       </c>
     </row>
     <row r="27">
@@ -3190,22 +2954,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Investing activity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fair value of shares issued for resource properties</t>
+          <t>Acquisition of resource properties</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="5" t="n">
+        <v>-0.015</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.192381</v>
+        <v>-0.385</v>
       </c>
     </row>
     <row r="28">
@@ -3216,24 +2978,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Investing activity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Balance, April 11, 2024 (incorporation) 1 - - -</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in investing activity</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.385</v>
       </c>
     </row>
     <row r="29">
@@ -3244,24 +3006,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cancellation of share (1) - - -</t>
+          <t>Proceeds from private placement of units</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="5" t="n">
+        <v>0.910035</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>3.60577</v>
       </c>
     </row>
     <row r="30">
@@ -3272,22 +3030,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 7,000,000 392,500 - -</t>
+          <t>Proceeds from the issuance of flow-through shares</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>0.3925</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.6005</v>
       </c>
     </row>
     <row r="31">
@@ -3298,22 +3056,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shares issued for flow-through common shares 9,075,000 181,500 - -</t>
+          <t>Proceeds from shares to be issued</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" s="5" t="n">
-        <v>0.1815</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.0002</v>
       </c>
     </row>
     <row r="32">
@@ -3324,22 +3082,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Initial recognition of flow-through premium liability - (136,125) - -</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>-0.136125</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from exercise of stock option</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.06525</v>
       </c>
     </row>
     <row r="33">
@@ -3350,22 +3112,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Special warrants issued for private placement - - - 335,398</t>
+          <t>Proceeds from exercise of warrants</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>0.335398</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1.606052</v>
       </c>
     </row>
     <row r="34">
@@ -3376,22 +3138,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Share issuance cost - (30,924) - -</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
-        <v>-0.030924</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.031561</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>-0.409049</v>
       </c>
     </row>
     <row r="35">
@@ -3402,24 +3166,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net loss for the period - - - -</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-0.089353</v>
+        <v>0.878474</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.089353</v>
+        <v>7.468723</v>
       </c>
     </row>
     <row r="36">
@@ -3430,20 +3194,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Balance, January 31, 2025 16,075,000 406,951 - 335,398</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>0.652996</v>
+        <v>0.700088</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.089353</v>
+        <v>4.396327</v>
       </c>
     </row>
     <row r="37">
@@ -3454,24 +3222,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Conversion of special warrants 3,360,350 335,398 - (335,398)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of the period</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="5" t="n">
+        <v>0.700088</v>
       </c>
     </row>
     <row r="38">
@@ -3482,22 +3252,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Units issued for private placement 10,302,200 3,605,770 - -</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of the period</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>3.60577</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.700088</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>5.096415</v>
       </c>
     </row>
     <row r="39">
@@ -3508,22 +3280,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Flow-through shares issued in private placement 2,364,091 2,600,500 - -</t>
+          <t>Cash received from interest</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>2.6005</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.009286000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3534,17 +3306,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shares issued for resource properties 336,986 192,381 - -</t>
+          <t>Cash paid for income taxes</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" s="5" t="n">
-        <v>0.192381</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,21 +3334,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 604,962</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0.604962</v>
+          <t>Cash paid for the interest</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3590,22 +3362,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of stock option 145,000 99,467 - (34,217)</t>
+          <t>Fair value of finders warrants issued</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>0.06525</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0.444085</v>
       </c>
     </row>
     <row r="43">
@@ -3616,22 +3388,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of warrants 4,908,700 1,742,748 - (136,696)</t>
+          <t>Fair value of shares issued for resource properties</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>1.606052</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.192381</v>
       </c>
     </row>
     <row r="44">
@@ -3647,12 +3419,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shares to be issued - - 200 -</t>
+          <t>Balance, April 11, 2024 (incorporation) 1 - - -</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>0.0002</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3673,12 +3447,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Share issuance cost - (853,134) - 444,085</t>
+          <t>Cancellation of share (1) - - -</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>-0.409049</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3699,19 +3475,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Shares issued for private placement 7,000,000 392,500 - -</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>-2.605752</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>-2.605752</v>
+        <v>0.3925</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3727,384 +3501,812 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Balance, January 31, 2026 37,492,327 8,130,081 200 878,134</t>
+          <t>Shares issued for flow-through common shares 9,075,000 181,500 - -</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>6.31331</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>-2.695105</v>
+        <v>0.1815</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Initial recognition of flow-through premium liability - (136,125) - -</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>1.1e-05</v>
+        <v>-0.136125</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses 5</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Special warrants issued for private placement - - - 335,398</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
-        <v>0.178046</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>1.02543</v>
+        <v>0.335398</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Investor relations and marketing</t>
+          <t>Share issuance cost - (30,924) - -</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0.575089</v>
+      <c r="E50" s="5" t="n">
+        <v>-0.030924</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Listing fees</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period - - - -</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-0.089353</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.067913</v>
+        <v>-0.089353</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Management compensation 8</t>
+          <t>Balance, January 31, 2025 16,075,000 406,951 - 335,398</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="5" t="n">
+        <v>0.652996</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.164402</v>
+        <v>-0.089353</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.000728</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.036014</v>
+          <t>Conversion of special warrants 3,360,350 335,398 - (335,398)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Units issued for private placement 10,302,200 3,605,770 - -</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.031825</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.173631</v>
+        <v>3.60577</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Share-based compensation 7, 8</t>
+          <t>Flow-through shares issued in private placement 2,364,091 2,600,500 - -</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.604962</v>
+      <c r="E55" s="5" t="n">
+        <v>2.6005</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Shares issued for resource properties 336,986 192,381 - -</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="n">
-        <v>-0.210599</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>-2.647441</v>
+        <v>0.192381</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Share-based compensation - - - 604,962</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0.02681</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.604962</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium</t>
+          <t>Shares issued on exercise of stock option 145,000 99,467 - (34,217)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0.121246</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.014879</v>
+        <v>0.06525</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued on exercise of warrants 4,908,700 1,742,748 - (136,696)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>-0.089353</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>-2.605752</v>
+        <v>1.606052</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss per share - Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Shares to be issued - - 200 -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>-1e-07</v>
+        <v>0.0002</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Share issuance cost - (853,134) - 444,085</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
+        <v>-0.409049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>-2.605752</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-2.605752</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2026 37,492,327 8,130,081 200 878,134</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>6.31331</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-2.695105</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Period from</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>1.1e-05</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenses 5</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>0.178046</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>1.02543</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Investor relations and marketing</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.575089</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Listing fees</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.067913</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Management compensation 8</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.164402</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.000728</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.036014</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0.031825</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.173631</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Share-based compensation 7, 8</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.604962</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>-0.210599</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-2.647441</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.02681</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Amortization of flow-through premium</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.121246</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.014879</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>-0.089353</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-2.605752</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Loss per share - Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>-1e-07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
         <v>13.483108</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F77" s="5" t="n">
         <v>25.99981</v>
       </c>
     </row>
